--- a/Empregos_por_Divisao_CNAE_RAIS_Capanema.xlsx
+++ b/Empregos_por_Divisao_CNAE_RAIS_Capanema.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH62"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,403 +471,291 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vínculos empregatícios ativos em 31/12. Fonte: RAIS/MTE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Seção</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Nome Seção</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Divisão</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Nome Divisão</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2001</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2003</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2005</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2007</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2009</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2011</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2013</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2015</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2017</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2019</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2021</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2023</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2025</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2001</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2003</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2005</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2007</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2009</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2011</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2013</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2015</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2017</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2019</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2021</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2023</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2025</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr">
-        <is>
-          <t>QL Médio</t>
-        </is>
-      </c>
-      <c r="AF3" s="2" t="inlineStr">
-        <is>
-          <t>Representat. (%)</t>
-        </is>
-      </c>
-      <c r="AG3" s="2" t="inlineStr">
-        <is>
-          <t>Cresc. 5 anos (%)</t>
-        </is>
-      </c>
-      <c r="AH3" s="2" t="inlineStr">
-        <is>
-          <t>Consistência (0-12)</t>
+          <t>Vínculos empregatícios ativos em 31/12. QL calculado no nível de Divisão. Fonte: RAIS/MTE.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AGRICULTURA, PECUÁRIA E SERVIÇOS RELACIONADOS</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>109</v>
-      </c>
-      <c r="F4" t="n">
-        <v>208</v>
-      </c>
-      <c r="G4" t="n">
-        <v>791</v>
-      </c>
-      <c r="H4" t="n">
-        <v>427</v>
-      </c>
-      <c r="I4" t="n">
-        <v>387</v>
-      </c>
-      <c r="J4" t="n">
-        <v>454</v>
-      </c>
-      <c r="K4" t="n">
-        <v>557</v>
-      </c>
-      <c r="L4" t="n">
-        <v>521</v>
-      </c>
-      <c r="M4" t="n">
-        <v>491</v>
-      </c>
-      <c r="N4" t="n">
-        <v>468</v>
-      </c>
-      <c r="O4" t="n">
-        <v>603</v>
-      </c>
-      <c r="P4" t="n">
-        <v>874</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>850</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.904005</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.600298</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4.116948</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.163407</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2.172241</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.345123</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.54644</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.398446</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.216855</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.317096</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3.430988</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.183243</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4.655371</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.850035</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>13.765182</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>81.623932</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>6/12</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Seção</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Nome Seção</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Divisão</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Nome Divisão</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2001</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2003</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2005</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2007</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2009</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2011</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2013</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2015</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2017</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2019</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2021</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2023</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2025</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2001</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2003</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2005</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2007</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2009</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2011</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2013</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2015</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2017</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2019</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2021</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2023</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2025</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>QL Médio</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>Representat. (%)</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>Cresc. 5 anos (%)</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>Consistência (0-12)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
+          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS ALIMENTÍCIOS</t>
+          <t>AGRICULTURA, PECUÁRIA E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>208</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>791</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>427</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>454</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>557</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>521</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>491</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>468</v>
       </c>
       <c r="O5" t="n">
-        <v>12</v>
+        <v>603</v>
       </c>
       <c r="P5" t="n">
-        <v>43</v>
+        <v>874</v>
       </c>
       <c r="Q5" t="n">
-        <v>37</v>
+        <v>850</v>
       </c>
       <c r="R5" t="n">
-        <v>0.623844</v>
+        <v>1.904005</v>
       </c>
       <c r="S5" t="n">
-        <v>0.020264</v>
+        <v>1.600298</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.116948</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.163407</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.172241</v>
       </c>
       <c r="W5" t="n">
-        <v>0.219544</v>
+        <v>2.345123</v>
       </c>
       <c r="X5" t="n">
-        <v>0.077303</v>
+        <v>2.54644</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.017165</v>
+        <v>2.398446</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.007656</v>
+        <v>2.216855</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.028191</v>
+        <v>3.317096</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.093278</v>
+        <v>3.430988</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.296051</v>
+        <v>4.183243</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.246514</v>
+        <v>4.655371</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.12537</v>
+        <v>2.850035</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.59919</v>
+        <v>13.765182</v>
       </c>
       <c r="AG5" t="n">
-        <v>1133.333333</v>
+        <v>81.623932</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -883,18 +771,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS TÊXTEIS</t>
+          <t>FABRICAÇÃO DE PRODUTOS ALIMENTÍCIOS</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -906,34 +794,34 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>22</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.623844</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.020264</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -945,41 +833,41 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.110012</v>
+        <v>0.219544</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.077303</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.173656</v>
+        <v>0.017165</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>0.007656</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.84139</v>
+        <v>0.028191</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.401302</v>
+        <v>0.093278</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>0.296051</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>0.246514</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.117412</v>
+        <v>0.12537</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.59919</v>
       </c>
       <c r="AG6" t="n">
-        <v>-100</v>
+        <v>1133.333333</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -995,60 +883,60 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CONFECÇÃO DE ARTIGOS DO VESTUÁRIO E ACESSÓRIOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS TÊXTEIS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.817123</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.17475</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.50671</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1057,43 +945,41 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.110012</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.173656</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.195699</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>0.84139</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>0.401302</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.249448</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.390558</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.41033</v>
+        <v>0.117412</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.048583</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-100</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1109,21 +995,21 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PREPARAÇÃO DE COUROS E FABRICAÇÃO DE ARTEFATOS DE COURO, ARTIGOS PARA VIAGEM E CALÇADOS</t>
+          <t>CONFECÇÃO DE ARTIGOS DO VESTUÁRIO E ACESSÓRIOS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1141,28 +1027,28 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>2</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="P8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>29</v>
-      </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.817123</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.17475</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.50671</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1180,28 +1066,30 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>0.195699</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.472584</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.609127</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.019785</v>
+        <v>0.249448</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.076643</v>
+        <v>0.390558</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.629088</v>
+        <v>0.41033</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.469636</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1350</v>
+        <v>0.048583</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1221,103 +1109,103 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DE MADEIRA</t>
+          <t>PREPARAÇÃO DE COUROS E FABRICAÇÃO DE ARTEFATOS DE COURO, ARTIGOS PARA VIAGEM E CALÇADOS</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1169</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1169</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1370</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>752</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>566</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>479</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>388</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>437</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>330</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>307</v>
+        <v>29</v>
       </c>
       <c r="R9" t="n">
-        <v>9.257167000000001</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4.773881</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>5.089804</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>13.701707</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>18.404257</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>17.341569</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>19.546145</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.69223</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.175307</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.268503</v>
+        <v>0.472584</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.358681</v>
+        <v>0.609127</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.136768</v>
+        <v>2.019785</v>
       </c>
       <c r="AD9" t="n">
-        <v>11.881453</v>
+        <v>5.076643</v>
       </c>
       <c r="AE9" t="n">
-        <v>12.971344</v>
+        <v>0.629088</v>
       </c>
       <c r="AF9" t="n">
-        <v>4.97166</v>
+        <v>0.469636</v>
       </c>
       <c r="AG9" t="n">
-        <v>-20.876289</v>
+        <v>1350</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1333,99 +1221,99 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IMPRESSÃO E REPRODUÇÃO DE GRAVAÇÕES</t>
+          <t>FABRICAÇÃO DE PRODUTOS DE MADEIRA</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1169</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1169</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>1370</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>752</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>566</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>510</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>479</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>331</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>277</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>388</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>330</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>307</v>
       </c>
       <c r="R10" t="n">
-        <v>0.783656</v>
+        <v>9.257167000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>0.261037</v>
+        <v>4.773881</v>
       </c>
       <c r="T10" t="n">
-        <v>0.218573</v>
+        <v>5.089804</v>
       </c>
       <c r="U10" t="n">
-        <v>1.200984</v>
+        <v>13.701707</v>
       </c>
       <c r="V10" t="n">
-        <v>1.096377</v>
+        <v>18.404257</v>
       </c>
       <c r="W10" t="n">
-        <v>0.443294</v>
+        <v>17.341569</v>
       </c>
       <c r="X10" t="n">
-        <v>0.414095</v>
+        <v>19.546145</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.403496</v>
+        <v>15.69223</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.423474</v>
+        <v>14.175307</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.603908</v>
+        <v>14.268503</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.586623</v>
+        <v>13.358681</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.6332449999999999</v>
+        <v>11.136768</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.475968</v>
+        <v>11.881453</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.580364</v>
+        <v>12.971344</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.048583</v>
+        <v>4.97166</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-20.876289</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -1436,226 +1324,224 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
+          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IMPRESSÃO E REPRODUÇÃO DE GRAVAÇÕES</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>PRODUÇÃO FLORESTAL</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>21</v>
-      </c>
       <c r="F11" t="n">
-        <v>406</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>566</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1442</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>1099</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>997</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>618</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>601</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>568</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>397</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>395</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>534</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.479604</v>
+        <v>0.783656</v>
       </c>
       <c r="S11" t="n">
-        <v>12.515614</v>
+        <v>0.261037</v>
       </c>
       <c r="T11" t="n">
-        <v>14.715748</v>
+        <v>0.218573</v>
       </c>
       <c r="U11" t="n">
-        <v>27.026802</v>
+        <v>1.200984</v>
       </c>
       <c r="V11" t="n">
-        <v>31.060373</v>
+        <v>1.096377</v>
       </c>
       <c r="W11" t="n">
-        <v>27.150699</v>
+        <v>0.443294</v>
       </c>
       <c r="X11" t="n">
-        <v>20.982314</v>
+        <v>0.414095</v>
       </c>
       <c r="Y11" t="n">
-        <v>26.906068</v>
+        <v>0.403496</v>
       </c>
       <c r="Z11" t="n">
-        <v>29.301968</v>
+        <v>0.423474</v>
       </c>
       <c r="AA11" t="n">
-        <v>38.086853</v>
+        <v>0.603908</v>
       </c>
       <c r="AB11" t="n">
-        <v>35.387878</v>
+        <v>0.586623</v>
       </c>
       <c r="AC11" t="n">
-        <v>30.538381</v>
+        <v>0.6332449999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>39.469198</v>
+        <v>0.475968</v>
       </c>
       <c r="AE11" t="n">
-        <v>25.740115</v>
+        <v>0.580364</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.647773000000001</v>
+        <v>0.048583</v>
       </c>
       <c r="AG11" t="n">
-        <v>34.508816</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
+          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS QUÍMICOS</t>
+          <t>PRODUÇÃO FLORESTAL</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>406</v>
       </c>
       <c r="G12" t="n">
-        <v>363</v>
+        <v>566</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>1442</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1099</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>997</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>618</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>568</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>534</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.479604</v>
       </c>
       <c r="S12" t="n">
-        <v>2.060781</v>
+        <v>12.515614</v>
       </c>
       <c r="T12" t="n">
-        <v>8.285253000000001</v>
+        <v>14.715748</v>
       </c>
       <c r="U12" t="n">
-        <v>1.552396</v>
+        <v>27.026802</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>31.060373</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>27.150699</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>20.982314</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>26.906068</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>29.301968</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>38.086853</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>35.387878</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>30.538381</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>39.469198</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.915264</v>
+        <v>25.740115</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>8.647773000000001</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>34.508816</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -1671,103 +1557,105 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DE MINERAIS NÃO-METÁLICOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS QUÍMICOS</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>363</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.060781</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>8.285253000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.022907</v>
+        <v>1.552396</v>
       </c>
       <c r="V13" t="n">
-        <v>0.348239</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.661173</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6740119999999999</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.45502</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.538389</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.320866</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.027869</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.821905</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.771729</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.587855</v>
+        <v>0.915264</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.37247</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>-20.689655</v>
+        <v>0</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -1783,11 +1671,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DE METAL, EXCETO MÁQUINAS E EQUIPAMENTOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS DE MINERAIS NÃO-METÁLICOS</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1800,34 +1688,34 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="P14" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1839,43 +1727,43 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.022907</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.348239</v>
       </c>
       <c r="W14" t="n">
-        <v>0.067896</v>
+        <v>1.661173</v>
       </c>
       <c r="X14" t="n">
-        <v>0.205912</v>
+        <v>0.6740119999999999</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.154199</v>
+        <v>0.45502</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.119642</v>
+        <v>0.538389</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.145304</v>
+        <v>1.320866</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.057218</v>
+        <v>1.027869</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.776095</v>
+        <v>0.821905</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.948201</v>
+        <v>0.771729</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.190344</v>
+        <v>0.587855</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.356275</v>
+        <v>0.37247</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>-20.689655</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -1895,11 +1783,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE MÁQUINAS, APARELHOS E MATERIAIS ELÉTRICOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS DE METAL, EXCETO MÁQUINAS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1918,28 +1806,28 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1957,43 +1845,41 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.067896</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.205912</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.32185</v>
+        <v>0.154199</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>0.119642</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>0.145304</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>0.057218</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>0.776095</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>0.948201</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.024758</v>
+        <v>0.190344</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.356275</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -2009,11 +1895,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
+          <t>FABRICAÇÃO DE MÁQUINAS, APARELHOS E MATERIAIS ELÉTRICOS</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2038,19 +1924,19 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2077,25 +1963,25 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>23.129299</v>
+        <v>0.32185</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.33936</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.152751</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.162224</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.291049</v>
+        <v>0.024758</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2107,7 +1993,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -2123,11 +2009,11 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE VEÍCULOS AUTOMOTORES, REBOQUES E CARROCERIAS</t>
+          <t>FABRICAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2143,31 +2029,31 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>102</v>
+      </c>
+      <c r="M17" t="n">
+        <v>81</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2182,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.90594</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -2191,28 +2077,28 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>23.129299</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>19.33936</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>0.152751</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.899536</v>
+        <v>0.162224</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.489771</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.176557</v>
+        <v>3.291049</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.097166</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -2237,33 +2123,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE MÓVEIS</t>
+          <t>FABRICAÇÃO DE VEÍCULOS AUTOMOTORES, REBOQUES E CARROCERIAS</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2275,34 +2161,34 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.253742</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.474359</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.90594</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.181608</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2314,19 +2200,19 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.113035</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.09761300000000001</v>
+        <v>0.899536</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.267502</v>
+        <v>0.489771</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.106758</v>
+        <v>0.176557</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.048583</v>
+        <v>0.097166</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -2335,7 +2221,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -2351,21 +2237,21 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DIVERSOS</t>
+          <t>FABRICAÇÃO DE MÓVEIS</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2377,19 +2263,19 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -2401,10 +2287,10 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.253742</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.474359</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2416,10 +2302,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.181608</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.451649</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -2428,16 +2314,16 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>0.113035</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.124427</v>
+        <v>0.09761300000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.37344</v>
+        <v>0.267502</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.07303999999999999</v>
+        <v>0.106758</v>
       </c>
       <c r="AF19" t="n">
         <v>0.048583</v>
@@ -2449,7 +2335,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -2465,11 +2351,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO, REPARAÇÃO E INSTALAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS DIVERSOS</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2485,311 +2371,313 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>20</v>
-      </c>
-      <c r="M20" t="n">
-        <v>14</v>
-      </c>
-      <c r="N20" t="n">
-        <v>22</v>
-      </c>
-      <c r="O20" t="n">
-        <v>20</v>
-      </c>
-      <c r="P20" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>13</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.451649</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.124427</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.07303999999999999</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.048583</v>
+      </c>
+      <c r="AG20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.515184</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.47861</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.815563</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.222216</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.442988</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.374259</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.7623490000000001</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.595258</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.7672020000000001</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0.210526</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>-40.909091</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ELETRICIDADE E GÁS</t>
+          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ELETRICIDADE, GÁS E OUTRAS UTILIDADES</t>
+          <t>MANUTENÇÃO, REPARAÇÃO E INSTALAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S21" t="n">
-        <v>0.28434</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.205871</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.120332</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.163207</v>
+        <v>0.515184</v>
       </c>
       <c r="W21" t="n">
-        <v>0.23634</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.07205300000000001</v>
+        <v>0.47861</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.071616</v>
+        <v>1.815563</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.222216</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.442988</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.374259</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>0.7623490000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.188135</v>
+        <v>0.595258</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.103223</v>
+        <v>0.7672020000000001</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.064777</v>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.210526</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-40.909091</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
+          <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CAPTAÇÃO, TRATAMENTO E DISTRIBUIÇÃO DE ÁGUA</t>
+          <t>ELETRICIDADE, GÁS E OUTRAS UTILIDADES</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.513168</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.906146</v>
+        <v>0.28434</v>
       </c>
       <c r="T22" t="n">
-        <v>1.885348</v>
+        <v>0.205871</v>
       </c>
       <c r="U22" t="n">
-        <v>1.048255</v>
+        <v>0.120332</v>
       </c>
       <c r="V22" t="n">
-        <v>5.701162</v>
+        <v>0.163207</v>
       </c>
       <c r="W22" t="n">
-        <v>5.677809</v>
+        <v>0.23634</v>
       </c>
       <c r="X22" t="n">
-        <v>7.057023</v>
+        <v>0.07205300000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.729242</v>
+        <v>0.071616</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.327989</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.41523</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.200786</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.02617</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.760852</v>
+        <v>0.188135</v>
       </c>
       <c r="AE22" t="n">
-        <v>3.557629</v>
+        <v>0.103223</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.226721</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>-66.666667</v>
+        <v>0.064777</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -2805,217 +2693,217 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>COLETA, TRATAMENTO E DISPOSIÇÃO DE RESÍDUOS; RECUPERAÇÃO DE MATERIAIS</t>
+          <t>CAPTAÇÃO, TRATAMENTO E DISTRIBUIÇÃO DE ÁGUA</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L23" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.513168</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.906146</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.885348</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.048255</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5.701162</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>5.677809</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>7.057023</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.40963</v>
+        <v>5.729242</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>7.327989</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.41523</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>4.200786</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.02617</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>0.760852</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.339202</v>
+        <v>3.557629</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.226721</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-66.666667</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO</t>
+          <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE EDIFÍCIOS</t>
+          <t>COLETA, TRATAMENTO E DISPOSIÇÃO DE RESÍDUOS; RECUPERAÇÃO DE MATERIAIS</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M24" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.014635</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.04728</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.045769</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.072052</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0.079359</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.126618</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.132308</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.334739</v>
+        <v>4.40963</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.951838</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.342194</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.529651</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.303595</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.64782</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.279066</v>
+        <v>0.339202</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.036437</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>178.26087</v>
+        <v>0</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -3031,103 +2919,103 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OBRAS DE INFRA-ESTRUTURA</t>
+          <t>CONSTRUÇÃO DE EDIFÍCIOS</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I25" t="n">
+        <v>11</v>
+      </c>
+      <c r="J25" t="n">
         <v>21</v>
       </c>
-      <c r="J25" t="n">
-        <v>19</v>
-      </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M25" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="N25" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="O25" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="P25" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.014635</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>0.04728</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.045769</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>0.072052</v>
       </c>
       <c r="V25" t="n">
-        <v>0.19842</v>
+        <v>0.079359</v>
       </c>
       <c r="W25" t="n">
-        <v>0.149475</v>
+        <v>0.126618</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.132308</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>0.334739</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.198546</v>
+        <v>0.951838</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.154103</v>
+        <v>0.342194</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.090447</v>
+        <v>0.529651</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.347589</v>
+        <v>0.303595</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.049862</v>
+        <v>0.64782</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.091419</v>
+        <v>0.279066</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.080972</v>
+        <v>1.036437</v>
       </c>
       <c r="AG25" t="n">
-        <v>-44.444444</v>
+        <v>178.26087</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>10/12</t>
         </is>
       </c>
     </row>
@@ -3143,11 +3031,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SERVIÇOS ESPECIALIZADOS PARA CONSTRUÇÃO</t>
+          <t>OBRAS DE INFRA-ESTRUTURA</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3163,31 +3051,31 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="Q26" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3202,156 +3090,156 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0.061755</v>
+        <v>0.19842</v>
       </c>
       <c r="W26" t="n">
-        <v>0.023001</v>
+        <v>0.149475</v>
       </c>
       <c r="X26" t="n">
-        <v>0.138451</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.321076</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.204051</v>
+        <v>0.198546</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.119591</v>
+        <v>0.154103</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.059523</v>
+        <v>0.090447</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.046286</v>
+        <v>0.347589</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.150037</v>
+        <v>0.049862</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.08644399999999999</v>
+        <v>0.091419</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.194332</v>
+        <v>0.080972</v>
       </c>
       <c r="AG26" t="n">
-        <v>100</v>
+        <v>-44.444444</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
+          <t>CONSTRUÇÃO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>COMÉRCIO E REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
+          <t>SERVIÇOS ESPECIALIZADOS PARA CONSTRUÇÃO</t>
         </is>
       </c>
       <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>12</v>
+      </c>
+      <c r="L27" t="n">
+        <v>28</v>
+      </c>
+      <c r="M27" t="n">
         <v>18</v>
       </c>
-      <c r="F27" t="n">
-        <v>44</v>
-      </c>
-      <c r="G27" t="n">
-        <v>62</v>
-      </c>
-      <c r="H27" t="n">
-        <v>59</v>
-      </c>
-      <c r="I27" t="n">
-        <v>72</v>
-      </c>
-      <c r="J27" t="n">
-        <v>147</v>
-      </c>
-      <c r="K27" t="n">
-        <v>157</v>
-      </c>
-      <c r="L27" t="n">
-        <v>131</v>
-      </c>
-      <c r="M27" t="n">
-        <v>121</v>
-      </c>
       <c r="N27" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="R27" t="n">
-        <v>0.5815360000000001</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.775958</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.682957</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0.659133</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8026</v>
+        <v>0.061755</v>
       </c>
       <c r="W27" t="n">
-        <v>1.595317</v>
+        <v>0.023001</v>
       </c>
       <c r="X27" t="n">
-        <v>1.541927</v>
+        <v>0.138451</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3517</v>
+        <v>0.321076</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.390706</v>
+        <v>0.204051</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.83327</v>
+        <v>0.119591</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.814212</v>
+        <v>0.059523</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.943433</v>
+        <v>0.046286</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.949634</v>
+        <v>0.150037</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.9940290000000001</v>
+        <v>0.08644399999999999</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.813765</v>
+        <v>0.194332</v>
       </c>
       <c r="AG27" t="n">
-        <v>57.746479</v>
+        <v>100</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -3367,103 +3255,103 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>COMÉRCIO POR ATACADO, EXCETO VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
+          <t>COMÉRCIO E REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="G28" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="H28" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="I28" t="n">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="J28" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="K28" t="n">
-        <v>323</v>
+        <v>157</v>
       </c>
       <c r="L28" t="n">
-        <v>349</v>
+        <v>131</v>
       </c>
       <c r="M28" t="n">
-        <v>430</v>
+        <v>121</v>
       </c>
       <c r="N28" t="n">
-        <v>302</v>
+        <v>71</v>
       </c>
       <c r="O28" t="n">
-        <v>554</v>
+        <v>83</v>
       </c>
       <c r="P28" t="n">
-        <v>424</v>
+        <v>110</v>
       </c>
       <c r="Q28" t="n">
-        <v>440</v>
+        <v>112</v>
       </c>
       <c r="R28" t="n">
-        <v>0.129903</v>
+        <v>0.5815360000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>0.200245</v>
+        <v>0.775958</v>
       </c>
       <c r="T28" t="n">
-        <v>0.312178</v>
+        <v>0.682957</v>
       </c>
       <c r="U28" t="n">
-        <v>0.447445</v>
+        <v>0.659133</v>
       </c>
       <c r="V28" t="n">
-        <v>0.844087</v>
+        <v>0.8026</v>
       </c>
       <c r="W28" t="n">
-        <v>0.995742</v>
+        <v>1.595317</v>
       </c>
       <c r="X28" t="n">
-        <v>2.037789</v>
+        <v>1.541927</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.080499</v>
+        <v>1.3517</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.541757</v>
+        <v>1.390706</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.248107</v>
+        <v>0.83327</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.16912</v>
+        <v>0.814212</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.249392</v>
+        <v>0.943433</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.353346</v>
+        <v>0.949634</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.508431</v>
+        <v>0.9940290000000001</v>
       </c>
       <c r="AF28" t="n">
-        <v>7.125506</v>
+        <v>1.813765</v>
       </c>
       <c r="AG28" t="n">
-        <v>45.695364</v>
+        <v>57.746479</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
@@ -3479,99 +3367,99 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>COMÉRCIO VAREJISTA</t>
+          <t>COMÉRCIO POR ATACADO, EXCETO VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>283</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
-        <v>327</v>
+        <v>22</v>
       </c>
       <c r="G29" t="n">
-        <v>449</v>
+        <v>44</v>
       </c>
       <c r="H29" t="n">
-        <v>458</v>
+        <v>64</v>
       </c>
       <c r="I29" t="n">
-        <v>463</v>
+        <v>113</v>
       </c>
       <c r="J29" t="n">
-        <v>578</v>
+        <v>132</v>
       </c>
       <c r="K29" t="n">
-        <v>763</v>
+        <v>323</v>
       </c>
       <c r="L29" t="n">
-        <v>749</v>
+        <v>349</v>
       </c>
       <c r="M29" t="n">
-        <v>671</v>
+        <v>430</v>
       </c>
       <c r="N29" t="n">
-        <v>777</v>
+        <v>302</v>
       </c>
       <c r="O29" t="n">
-        <v>863</v>
+        <v>554</v>
       </c>
       <c r="P29" t="n">
-        <v>995</v>
+        <v>424</v>
       </c>
       <c r="Q29" t="n">
-        <v>1043</v>
+        <v>440</v>
       </c>
       <c r="R29" t="n">
-        <v>1.074238</v>
+        <v>0.129903</v>
       </c>
       <c r="S29" t="n">
-        <v>0.655202</v>
+        <v>0.200245</v>
       </c>
       <c r="T29" t="n">
-        <v>0.651112</v>
+        <v>0.312178</v>
       </c>
       <c r="U29" t="n">
-        <v>0.715871</v>
+        <v>0.447445</v>
       </c>
       <c r="V29" t="n">
-        <v>0.760167</v>
+        <v>0.844087</v>
       </c>
       <c r="W29" t="n">
-        <v>0.896833</v>
+        <v>0.995742</v>
       </c>
       <c r="X29" t="n">
-        <v>1.068004</v>
+        <v>2.037789</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.065031</v>
+        <v>2.080499</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.018011</v>
+        <v>2.541757</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.34092</v>
+        <v>2.248107</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.200536</v>
+        <v>3.16912</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.307421</v>
+        <v>2.249392</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.410623</v>
+        <v>2.353346</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.012613</v>
+        <v>1.508431</v>
       </c>
       <c r="AF29" t="n">
-        <v>16.890688</v>
+        <v>7.125506</v>
       </c>
       <c r="AG29" t="n">
-        <v>34.234234</v>
+        <v>45.695364</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -3582,268 +3470,260 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
+          <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TRANSPORTE TERRESTRE</t>
+          <t>COMÉRCIO VAREJISTA</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>18</v>
+        <v>283</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>327</v>
       </c>
       <c r="G30" t="n">
-        <v>30</v>
+        <v>449</v>
       </c>
       <c r="H30" t="n">
-        <v>27</v>
+        <v>458</v>
       </c>
       <c r="I30" t="n">
-        <v>34</v>
+        <v>463</v>
       </c>
       <c r="J30" t="n">
-        <v>43</v>
+        <v>578</v>
       </c>
       <c r="K30" t="n">
-        <v>52</v>
+        <v>763</v>
       </c>
       <c r="L30" t="n">
-        <v>40</v>
+        <v>749</v>
       </c>
       <c r="M30" t="n">
-        <v>33</v>
+        <v>671</v>
       </c>
       <c r="N30" t="n">
-        <v>54</v>
+        <v>777</v>
       </c>
       <c r="O30" t="n">
-        <v>73</v>
+        <v>863</v>
       </c>
       <c r="P30" t="n">
-        <v>167</v>
+        <v>995</v>
       </c>
       <c r="Q30" t="n">
-        <v>194</v>
+        <v>1043</v>
       </c>
       <c r="R30" t="n">
-        <v>0.245178</v>
+        <v>1.074238</v>
       </c>
       <c r="S30" t="n">
-        <v>0.10481</v>
+        <v>0.655202</v>
       </c>
       <c r="T30" t="n">
-        <v>0.218523</v>
+        <v>0.651112</v>
       </c>
       <c r="U30" t="n">
-        <v>0.220431</v>
+        <v>0.715871</v>
       </c>
       <c r="V30" t="n">
-        <v>0.296696</v>
+        <v>0.760167</v>
       </c>
       <c r="W30" t="n">
-        <v>0.349205</v>
+        <v>0.896833</v>
       </c>
       <c r="X30" t="n">
-        <v>0.407659</v>
+        <v>1.068004</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.293599</v>
+        <v>1.065031</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.265683</v>
+        <v>1.018011</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.516506</v>
+        <v>1.34092</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.574533</v>
+        <v>1.200536</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.190082</v>
+        <v>1.307421</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.406843</v>
+        <v>1.410623</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.468442</v>
+        <v>1.012613</v>
       </c>
       <c r="AF30" t="n">
-        <v>3.1417</v>
+        <v>16.890688</v>
       </c>
       <c r="AG30" t="n">
-        <v>259.259259</v>
+        <v>34.234234</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>10/12</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS EXTRATIVAS</t>
+          <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EXTRAÇÃO DE CARVÃO MINERAL</t>
+          <t>TRANSPORTE TERRESTRE</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>0.245178</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>0.10481</v>
       </c>
       <c r="T31" t="n">
-        <v>8.832725</v>
+        <v>0.218523</v>
       </c>
       <c r="U31" t="n">
-        <v>14.697753</v>
+        <v>0.220431</v>
       </c>
       <c r="V31" t="n">
-        <v>6.760993</v>
+        <v>0.296696</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>0.349205</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.407659</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>0.293599</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>0.265683</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.516506</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.574533</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.190082</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.406843</v>
       </c>
       <c r="AE31" t="n">
-        <v>3.029147</v>
+        <v>0.468442</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3.1417</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>259.259259</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
+          <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ARMAZENAMENTO E ATIVIDADES AUXILIARES DOS TRANSPORTES</t>
+          <t>EXTRAÇÃO DE CARVÃO MINERAL</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3861,28 +3741,28 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.219432</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>8.832725</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>14.697753</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>6.760993</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -3899,20 +3779,26 @@
       <c r="AA32" t="n">
         <v>0</v>
       </c>
-      <c r="AB32" t="n">
-        <v>0.167452</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0.162641</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.191292</v>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AE32" t="n">
-        <v>0.133909</v>
+        <v>3.029147</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.842105</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -3921,7 +3807,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -3937,99 +3823,101 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CORREIO E OUTRAS ATIVIDADES DE ENTREGA</t>
+          <t>ARMAZENAMENTO E ATIVIDADES AUXILIARES DOS TRANSPORTES</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>6</v>
+      </c>
+      <c r="P33" t="n">
         <v>7</v>
       </c>
-      <c r="H33" t="n">
-        <v>6</v>
-      </c>
-      <c r="I33" t="n">
-        <v>7</v>
-      </c>
-      <c r="J33" t="n">
-        <v>5</v>
-      </c>
-      <c r="K33" t="n">
-        <v>9</v>
-      </c>
-      <c r="L33" t="n">
-        <v>8</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>5</v>
-      </c>
-      <c r="P33" t="n">
-        <v>5</v>
-      </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="R33" t="n">
-        <v>0.5663049999999999</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.324214</v>
+        <v>0.219432</v>
       </c>
       <c r="T33" t="n">
-        <v>0.399427</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0.339677</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0.460644</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.389092</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.649798</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.577066</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.215951</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.080766</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.35465</v>
+        <v>0.167452</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.343965</v>
+        <v>0.162641</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.34066</v>
+        <v>1.191292</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.387863</v>
+        <v>0.133909</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.080972</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>400</v>
+        <v>0.842105</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -4040,112 +3928,112 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ALOJAMENTO E ALIMENTAÇÃO</t>
+          <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ALOJAMENTO</t>
+          <t>CORREIO E OUTRAS ATIVIDADES DE ENTREGA</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="L34" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="M34" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>0.5663049999999999</v>
       </c>
       <c r="S34" t="n">
-        <v>0.152399</v>
+        <v>0.324214</v>
       </c>
       <c r="T34" t="n">
-        <v>0.062178</v>
+        <v>0.399427</v>
       </c>
       <c r="U34" t="n">
-        <v>0.321088</v>
+        <v>0.339677</v>
       </c>
       <c r="V34" t="n">
-        <v>0.306956</v>
+        <v>0.460644</v>
       </c>
       <c r="W34" t="n">
-        <v>1.306478</v>
+        <v>0.389092</v>
       </c>
       <c r="X34" t="n">
-        <v>1.195422</v>
+        <v>0.649798</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.499244</v>
+        <v>0.577066</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.578904</v>
+        <v>0.215951</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.058929</v>
+        <v>0.080766</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.861632</v>
+        <v>0.35465</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.203873</v>
+        <v>0.343965</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.907535</v>
+        <v>0.34066</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.958049</v>
+        <v>0.387863</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.421053</v>
+        <v>0.080972</v>
       </c>
       <c r="AG34" t="n">
-        <v>-44.680851</v>
+        <v>400</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -4161,99 +4049,99 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO</t>
+          <t>ALOJAMENTO</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="K35" t="n">
+        <v>40</v>
+      </c>
+      <c r="L35" t="n">
+        <v>49</v>
+      </c>
+      <c r="M35" t="n">
         <v>46</v>
       </c>
-      <c r="L35" t="n">
-        <v>42</v>
-      </c>
-      <c r="M35" t="n">
-        <v>43</v>
-      </c>
       <c r="N35" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="O35" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="P35" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="Q35" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>0.152399</v>
       </c>
       <c r="T35" t="n">
-        <v>0.133959</v>
+        <v>0.062178</v>
       </c>
       <c r="U35" t="n">
-        <v>0.341619</v>
+        <v>0.321088</v>
       </c>
       <c r="V35" t="n">
-        <v>0.27034</v>
+        <v>0.306956</v>
       </c>
       <c r="W35" t="n">
-        <v>0.8265439999999999</v>
+        <v>1.306478</v>
       </c>
       <c r="X35" t="n">
-        <v>0.47814</v>
+        <v>1.195422</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.435807</v>
+        <v>1.499244</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.513979</v>
+        <v>1.578904</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.497983</v>
+        <v>2.058929</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.213788</v>
+        <v>1.861632</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.512504</v>
+        <v>1.203873</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.398824</v>
+        <v>0.907535</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.355653</v>
+        <v>0.958049</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.890688</v>
+        <v>0.421053</v>
       </c>
       <c r="AG35" t="n">
-        <v>27.906977</v>
+        <v>-44.680851</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -4264,114 +4152,112 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EDIÇÃO E EDIÇÃO INTEGRADA À IMPRESSÃO</t>
+          <t>ALIMENTAÇÃO</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.817615</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>0.133959</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.341619</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.27034</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.8265439999999999</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.47814</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>0.435807</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>0.513979</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>0.497983</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>0.213788</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>0.512504</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>0.398824</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.062893</v>
+        <v>0.355653</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.890688</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>27.906977</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -4387,103 +4273,105 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TELECOMUNICAÇÕES</t>
+          <t>EDIÇÃO E EDIÇÃO INTEGRADA À IMPRESSÃO</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>0.817615</v>
       </c>
       <c r="T37" t="n">
-        <v>0.06918299999999999</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.426179</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.891284</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.40114</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.21697</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.856861</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.620131</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.368728</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.866693</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.961143</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.590639</v>
+        <v>0.062893</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.404858</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>-3.846154</v>
+        <v>0</v>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -4499,11 +4387,11 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ATIVIDADES DOS SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO</t>
+          <t>TELECOMUNICAÇÕES</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4513,37 +4401,37 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4552,52 +4440,50 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>0.06918299999999999</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.426179</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>0.891284</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>0.40114</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.069001</v>
+        <v>0.21697</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>0.856861</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.620131</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.091226</v>
+        <v>1.368728</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>0.866693</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>0.961143</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.08924799999999999</v>
+        <v>0.590639</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.404858</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>-3.846154</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
@@ -4613,11 +4499,11 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE PRESTAÇÃO DE SERVIÇOS DE INFORMAÇÃO</t>
+          <t>ATIVIDADES DOS SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4630,34 +4516,34 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>6</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4669,10 +4555,10 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0.132583</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0.265716</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -4681,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.069001</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -4690,19 +4576,19 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>0.091226</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.354758</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.562815</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.101221</v>
+        <v>0.08924799999999999</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.048583</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -4711,119 +4597,121 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
+          <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE SERVIÇOS FINANCEIROS</t>
+          <t>ATIVIDADES DE PRESTAÇÃO DE SERVIÇOS DE INFORMAÇÃO</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>0.433877</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.297892</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.360313</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0.314356</v>
+        <v>0.132583</v>
       </c>
       <c r="V40" t="n">
-        <v>0.566976</v>
+        <v>0.265716</v>
       </c>
       <c r="W40" t="n">
-        <v>0.870986</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.8403350000000001</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.19652</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.283256</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.328048</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.440312</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.549207</v>
+        <v>0.354758</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.660664</v>
+        <v>0.562815</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.934057</v>
+        <v>0.101221</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.214575</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>41.509434</v>
+        <v>0.048583</v>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -4839,123 +4727,123 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ATIVIDADES AUXILIARES DOS SERVIÇOS FINANCEIROS, SEGUROS, PREVIDÊNCIA COMPLEMENTAR E PLANOS DE SAÚDE</t>
+          <t>ATIVIDADES DE SERVIÇOS FINANCEIROS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="O41" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="P41" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>0.433877</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>0.297892</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>0.360313</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>0.314356</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.566976</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>0.870986</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.8403350000000001</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.251722</v>
+        <v>1.19652</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.345041</v>
+        <v>1.283256</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.351371</v>
+        <v>1.328048</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.11097</v>
+        <v>1.440312</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.6006629999999999</v>
+        <v>1.549207</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.851474</v>
+        <v>1.660664</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.270095</v>
+        <v>0.934057</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.097166</v>
+        <v>1.214575</v>
       </c>
       <c r="AG41" t="n">
-        <v>500</v>
+        <v>41.509434</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ATIVIDADES IMOBILIÁRIAS</t>
+          <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ATIVIDADES IMOBILIÁRIAS</t>
+          <t>ATIVIDADES AUXILIARES DOS SERVIÇOS FINANCEIROS, SEGUROS, PREVIDÊNCIA COMPLEMENTAR E PLANOS DE SAÚDE</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4977,25 +4865,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="P42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5016,150 +4904,150 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0.165509</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.411244</v>
+        <v>0.251722</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.199752</v>
+        <v>0.345041</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.474655</v>
+        <v>0.351371</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.197421</v>
+        <v>1.11097</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.7092540000000001</v>
+        <v>0.6006629999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.66889</v>
+        <v>0.851474</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.294363</v>
+        <v>0.270095</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.129555</v>
+        <v>0.097166</v>
       </c>
       <c r="AG42" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
+          <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ATIVIDADES JURÍDICAS, DE CONTABILIDADE E DE AUDITORIA</t>
+          <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
       <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>4</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4</v>
+      </c>
+      <c r="O43" t="n">
+        <v>14</v>
+      </c>
+      <c r="P43" t="n">
         <v>10</v>
       </c>
-      <c r="F43" t="n">
-        <v>10</v>
-      </c>
-      <c r="G43" t="n">
-        <v>23</v>
-      </c>
-      <c r="H43" t="n">
-        <v>18</v>
-      </c>
-      <c r="I43" t="n">
-        <v>17</v>
-      </c>
-      <c r="J43" t="n">
-        <v>30</v>
-      </c>
-      <c r="K43" t="n">
-        <v>35</v>
-      </c>
-      <c r="L43" t="n">
-        <v>48</v>
-      </c>
-      <c r="M43" t="n">
-        <v>46</v>
-      </c>
-      <c r="N43" t="n">
-        <v>40</v>
-      </c>
-      <c r="O43" t="n">
-        <v>43</v>
-      </c>
-      <c r="P43" t="n">
-        <v>52</v>
-      </c>
       <c r="Q43" t="n">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="R43" t="n">
-        <v>1.315174</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.744063</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1.420512</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.194271</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0.973736</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.467851</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.213483</v>
+        <v>0.165509</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.574899</v>
+        <v>0.411244</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.532373</v>
+        <v>0.199752</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.407866</v>
+        <v>0.474655</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.231146</v>
+        <v>1.197421</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.23425</v>
+        <v>0.7092540000000001</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.463157</v>
+        <v>0.66889</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.290214</v>
+        <v>0.294363</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.987854</v>
+        <v>0.129555</v>
       </c>
       <c r="AG43" t="n">
-        <v>52.5</v>
+        <v>100</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -5175,103 +5063,103 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE SEDES DE EMPRESAS E DE CONSULTORIA EM GESTÃO EMPRESARIAL</t>
+          <t>ATIVIDADES JURÍDICAS, DE CONTABILIDADE E DE AUDITORIA</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="Q44" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.315174</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>0.744063</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.420512</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.194271</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>0.973736</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.467851</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.213483</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.175377</v>
+        <v>1.574899</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.358728</v>
+        <v>1.532373</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.153055</v>
+        <v>1.407866</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.231146</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.132615</v>
+        <v>1.23425</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.685719</v>
+        <v>1.463157</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.19273</v>
+        <v>1.290214</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.178138</v>
+        <v>0.987854</v>
       </c>
       <c r="AG44" t="n">
-        <v>1000</v>
+        <v>52.5</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
@@ -5287,11 +5175,11 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ARQUITETURA E ENGENHARIA; TESTES E ANÁLISES TÉCNICAS</t>
+          <t>ATIVIDADES DE SEDES DE EMPRESAS E DE CONSULTORIA EM GESTÃO EMPRESARIAL</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5313,25 +5201,25 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5352,34 +5240,34 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0.09432500000000001</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.157726</v>
+        <v>1.175377</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.086192</v>
+        <v>0.358728</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.053959</v>
+        <v>0.153055</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.315674</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.077153</v>
+        <v>0.132615</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.074515</v>
+        <v>0.685719</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.066119</v>
+        <v>0.19273</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.048583</v>
+        <v>0.178138</v>
       </c>
       <c r="AG45" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -5399,11 +5287,11 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PESQUISA E DESENVOLVIMENTO CIENTÍFICO</t>
+          <t>SERVIÇOS DE ARQUITETURA E ENGENHARIA; TESTES E ANÁLISES TÉCNICAS</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5425,25 +5313,25 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P46" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5464,40 +5352,38 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>0.09432500000000001</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>0.157726</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>0.086192</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>0.053959</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>0.315674</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.29491</v>
+        <v>0.077153</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.129176</v>
+        <v>0.074515</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.263391</v>
+        <v>0.066119</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.161943</v>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.048583</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>200</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -5513,11 +5399,11 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PUBLICIDADE E PESQUISA DE MERCADO</t>
+          <t>PESQUISA E DESENVOLVIMENTO CIENTÍFICO</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5548,16 +5434,16 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5587,25 +5473,27 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.240397</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.22887</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.29491</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.129176</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.036097</v>
+        <v>0.263391</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>-100</v>
+        <v>0.161943</v>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -5625,11 +5513,11 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>OUTRAS ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
+          <t>PUBLICIDADE E PESQUISA DE MERCADO</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5642,34 +5530,34 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="n">
+      <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>5</v>
-      </c>
       <c r="P48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5681,69 +5569,67 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.040988</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.73214</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0.231655</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0.117724</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.156229</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.583939</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>0.240397</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.476546</v>
+        <v>0.22887</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.580228</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.053018</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.382497</v>
+        <v>0.036097</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.242915</v>
-      </c>
-      <c r="AG48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>-100</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
+          <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ALUGUÉIS NÃO-IMOBILIÁRIOS E GESTÃO DE ATIVOS INTANGÍVEIS NÃO-FINANCEIROS</t>
+          <t>OUTRAS ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5756,34 +5642,34 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
         <v>5</v>
       </c>
-      <c r="J49" t="n">
-        <v>4</v>
-      </c>
-      <c r="K49" t="n">
-        <v>11</v>
-      </c>
-      <c r="L49" t="n">
-        <v>9</v>
-      </c>
-      <c r="M49" t="n">
-        <v>21</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3</v>
-      </c>
-      <c r="O49" t="n">
-        <v>38</v>
-      </c>
       <c r="P49" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="Q49" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -5795,43 +5681,45 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.040988</v>
       </c>
       <c r="V49" t="n">
-        <v>0.328558</v>
+        <v>0.73214</v>
       </c>
       <c r="W49" t="n">
-        <v>0.146811</v>
+        <v>0.231655</v>
       </c>
       <c r="X49" t="n">
-        <v>0.576531</v>
+        <v>0.117724</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.471483</v>
+        <v>0.156229</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.085929</v>
+        <v>0.583939</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.181155</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.768064</v>
+        <v>0.476546</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.196614</v>
+        <v>0.580228</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.501302</v>
+        <v>1.053018</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.635111</v>
+        <v>0.382497</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.874494</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1700</v>
+        <v>0.242915</v>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -5851,105 +5739,103 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SELEÇÃO, AGENCIAMENTO E LOCAÇÃO DE MÃO-DE-OBRA</t>
+          <t>ALUGUÉIS NÃO-IMOBILIÁRIOS E GESTÃO DE ATIVOS INTANGÍVEIS NÃO-FINANCEIROS</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>19.700575</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.252715</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>0.328558</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>0.146811</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>0.576531</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>0.471483</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.085929</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>0.181155</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.768064</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.196614</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.501302</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.611792</v>
+        <v>0.635111</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.874494</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>1700</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -5965,24 +5851,24 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AGÊNCIAS DE VIAGENS, OPERADORES TURÍSTICOS E SERVIÇOS DE RESERVAS</t>
+          <t>SELEÇÃO, AGENCIAMENTO E LOCAÇÃO DE MÃO-DE-OBRA</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>515</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -6009,19 +5895,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.677908</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.7233810000000001</v>
+        <v>19.700575</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.252715</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -6048,13 +5934,13 @@
         <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.19292</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.199554</v>
+        <v>1.611792</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.016194</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -6063,34 +5949,34 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS EXTRATIVAS</t>
+          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EXTRAÇÃO DE MINERAIS NÃO-METÁLICOS</t>
+          <t>AGÊNCIAS DE VIAGENS, OPERADORES TURÍSTICOS E SERVIÇOS DE RESERVAS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -6123,13 +6009,13 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.677908</v>
       </c>
       <c r="S52" t="n">
-        <v>2.720477</v>
+        <v>0.7233810000000001</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
@@ -6162,13 +6048,13 @@
         <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>0.19292</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.209267</v>
+        <v>0.199554</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>0.016194</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -6184,27 +6070,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
+          <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE VIGILÂNCIA, SEGURANÇA E INVESTIGAÇÃO</t>
+          <t>EXTRAÇÃO DE MINERAIS NÃO-METÁLICOS</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -6231,19 +6117,19 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.720477</v>
       </c>
       <c r="T53" t="n">
         <v>0</v>
@@ -6270,19 +6156,19 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.065277</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.06795900000000001</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.128009</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0.020096</v>
+        <v>0.209267</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.178138</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -6291,7 +6177,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -6307,665 +6193,667 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ESCRITÓRIO, DE APOIO ADMINISTRATIVO E OUTROS SERVIÇOS PRESTADOS PRINCIPALMENTE ÀS EMPRESAS</t>
+          <t>ATIVIDADES DE VIGILÂNCIA, SEGURANÇA E INVESTIGAÇÃO</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>5</v>
+      </c>
+      <c r="P54" t="n">
         <v>6</v>
       </c>
-      <c r="K54" t="n">
-        <v>7</v>
-      </c>
-      <c r="L54" t="n">
-        <v>14</v>
-      </c>
-      <c r="M54" t="n">
-        <v>15</v>
-      </c>
-      <c r="N54" t="n">
-        <v>12</v>
-      </c>
-      <c r="O54" t="n">
-        <v>76</v>
-      </c>
-      <c r="P54" t="n">
-        <v>110</v>
-      </c>
       <c r="Q54" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="R54" t="n">
-        <v>0.026437</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.345353</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>0.469845</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>0.091738</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>0.245212</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0.149444</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0.154957</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.384801</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.332122</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.219358</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.825141</v>
+        <v>0.065277</v>
       </c>
       <c r="AC54" t="n">
-        <v>0.771462</v>
+        <v>0.06795900000000001</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.49259</v>
+        <v>0.128009</v>
       </c>
       <c r="AE54" t="n">
-        <v>0.346805</v>
+        <v>0.020096</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.311741</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>575</v>
+        <v>0.178138</v>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
+          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
+          <t>SERVIÇOS DE ESCRITÓRIO, DE APOIO ADMINISTRATIVO E OUTROS SERVIÇOS PRESTADOS PRINCIPALMENTE ÀS EMPRESAS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>483</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>1122</v>
+        <v>17</v>
       </c>
       <c r="G55" t="n">
-        <v>1362</v>
+        <v>32</v>
       </c>
       <c r="H55" t="n">
-        <v>1159</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>1594</v>
+        <v>9</v>
       </c>
       <c r="J55" t="n">
-        <v>1481</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>1834</v>
+        <v>7</v>
       </c>
       <c r="L55" t="n">
-        <v>1658</v>
+        <v>14</v>
       </c>
       <c r="M55" t="n">
-        <v>1594</v>
+        <v>15</v>
       </c>
       <c r="N55" t="n">
-        <v>1299</v>
+        <v>12</v>
       </c>
       <c r="O55" t="n">
-        <v>1373</v>
+        <v>76</v>
       </c>
       <c r="P55" t="n">
-        <v>1786</v>
+        <v>110</v>
       </c>
       <c r="Q55" t="n">
-        <v>1759</v>
+        <v>81</v>
       </c>
       <c r="R55" t="n">
-        <v>0.5784049999999999</v>
+        <v>0.026437</v>
       </c>
       <c r="S55" t="n">
-        <v>0.740063</v>
+        <v>0.345353</v>
       </c>
       <c r="T55" t="n">
-        <v>0.707754</v>
+        <v>0.469845</v>
       </c>
       <c r="U55" t="n">
-        <v>0.732387</v>
+        <v>0.091738</v>
       </c>
       <c r="V55" t="n">
-        <v>0.89181</v>
+        <v>0.245212</v>
       </c>
       <c r="W55" t="n">
-        <v>0.834413</v>
+        <v>0.149444</v>
       </c>
       <c r="X55" t="n">
-        <v>1.034553</v>
+        <v>0.154957</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.97373</v>
+        <v>0.384801</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.941526</v>
+        <v>0.332122</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.8478560000000001</v>
+        <v>0.219358</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.784398</v>
+        <v>0.825141</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.957722</v>
+        <v>0.771462</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.830109</v>
+        <v>0.49259</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.834979</v>
+        <v>0.346805</v>
       </c>
       <c r="AF55" t="n">
-        <v>28.48583</v>
+        <v>1.311741</v>
       </c>
       <c r="AG55" t="n">
-        <v>35.411855</v>
+        <v>575</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EDUCAÇÃO</t>
+          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EDUCAÇÃO</t>
+          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="F56" t="n">
-        <v>13</v>
+        <v>1122</v>
       </c>
       <c r="G56" t="n">
-        <v>20</v>
+        <v>1362</v>
       </c>
       <c r="H56" t="n">
-        <v>38</v>
+        <v>1159</v>
       </c>
       <c r="I56" t="n">
-        <v>32</v>
+        <v>1594</v>
       </c>
       <c r="J56" t="n">
-        <v>51</v>
+        <v>1481</v>
       </c>
       <c r="K56" t="n">
-        <v>13</v>
+        <v>1834</v>
       </c>
       <c r="L56" t="n">
-        <v>36</v>
+        <v>1658</v>
       </c>
       <c r="M56" t="n">
-        <v>34</v>
+        <v>1594</v>
       </c>
       <c r="N56" t="n">
-        <v>40</v>
+        <v>1299</v>
       </c>
       <c r="O56" t="n">
-        <v>50</v>
+        <v>1373</v>
       </c>
       <c r="P56" t="n">
-        <v>89</v>
+        <v>1786</v>
       </c>
       <c r="Q56" t="n">
-        <v>107</v>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1759</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.5784049999999999</v>
       </c>
       <c r="S56" t="n">
-        <v>0.145671</v>
+        <v>0.740063</v>
       </c>
       <c r="T56" t="n">
-        <v>0.1786</v>
+        <v>0.707754</v>
       </c>
       <c r="U56" t="n">
-        <v>0.266092</v>
+        <v>0.732387</v>
       </c>
       <c r="V56" t="n">
-        <v>0.281206</v>
+        <v>0.89181</v>
       </c>
       <c r="W56" t="n">
-        <v>0.375087</v>
+        <v>0.834413</v>
       </c>
       <c r="X56" t="n">
-        <v>0.079683</v>
+        <v>1.034553</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.190439</v>
+        <v>0.97373</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.165394</v>
+        <v>0.941526</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.227931</v>
+        <v>0.8478560000000001</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.290763</v>
+        <v>0.784398</v>
       </c>
       <c r="AC56" t="n">
-        <v>0.226945</v>
+        <v>0.957722</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.307651</v>
+        <v>0.830109</v>
       </c>
       <c r="AE56" t="n">
-        <v>0.227955</v>
+        <v>0.834979</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.732794</v>
+        <v>28.48583</v>
       </c>
       <c r="AG56" t="n">
-        <v>167.5</v>
+        <v>35.411855</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
+          <t>EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE ATENÇÃO À SAÚDE HUMANA</t>
+          <t>EDUCAÇÃO</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G57" t="n">
+        <v>20</v>
+      </c>
+      <c r="H57" t="n">
+        <v>38</v>
+      </c>
+      <c r="I57" t="n">
         <v>32</v>
       </c>
-      <c r="H57" t="n">
-        <v>23</v>
-      </c>
-      <c r="I57" t="n">
-        <v>25</v>
-      </c>
       <c r="J57" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K57" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="L57" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M57" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="N57" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="O57" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="P57" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="Q57" t="n">
-        <v>48</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.326381</v>
+        <v>107</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S57" t="n">
-        <v>0.253441</v>
+        <v>0.145671</v>
       </c>
       <c r="T57" t="n">
-        <v>0.257658</v>
+        <v>0.1786</v>
       </c>
       <c r="U57" t="n">
-        <v>0.199736</v>
+        <v>0.266092</v>
       </c>
       <c r="V57" t="n">
-        <v>0.218483</v>
+        <v>0.281206</v>
       </c>
       <c r="W57" t="n">
-        <v>0.144653</v>
+        <v>0.375087</v>
       </c>
       <c r="X57" t="n">
-        <v>0.209536</v>
+        <v>0.079683</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.197255</v>
+        <v>0.190439</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.070636</v>
+        <v>0.165394</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.449609</v>
+        <v>0.227931</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.226854</v>
+        <v>0.290763</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.219385</v>
+        <v>0.226945</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.192251</v>
+        <v>0.307651</v>
       </c>
       <c r="AE57" t="n">
-        <v>0.228144</v>
+        <v>0.227955</v>
       </c>
       <c r="AF57" t="n">
-        <v>0.777328</v>
+        <v>1.732794</v>
       </c>
       <c r="AG57" t="n">
-        <v>-22.580645</v>
+        <v>167.5</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
+          <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ATIVIDADES ESPORTIVAS E DE RECREAÇÃO E LAZER</t>
+          <t>ATIVIDADES DE ATENÇÃO À SAÚDE HUMANA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G58" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L58" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="M58" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N58" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="O58" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="P58" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="R58" t="n">
-        <v>0.19001</v>
+        <v>0.326381</v>
       </c>
       <c r="S58" t="n">
-        <v>0.062949</v>
+        <v>0.253441</v>
       </c>
       <c r="T58" t="n">
-        <v>0.206003</v>
+        <v>0.257658</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>0.199736</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>0.218483</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>0.144653</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>0.209536</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.331717</v>
+        <v>0.197255</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.478779</v>
+        <v>0.070636</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.505449</v>
+        <v>0.449609</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.835799</v>
+        <v>0.226854</v>
       </c>
       <c r="AC58" t="n">
-        <v>0.807243</v>
+        <v>0.219385</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.6794289999999999</v>
+        <v>0.192251</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.315183</v>
+        <v>0.228144</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.259109</v>
+        <v>0.777328</v>
       </c>
       <c r="AG58" t="n">
-        <v>166.666667</v>
+        <v>-22.580645</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
+          <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE ORGANIZAÇÕES ASSOCIATIVAS</t>
+          <t>ATIVIDADES ESPORTIVAS E DE RECREAÇÃO E LAZER</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>7</v>
+      </c>
+      <c r="M59" t="n">
         <v>10</v>
       </c>
-      <c r="G59" t="n">
-        <v>10</v>
-      </c>
-      <c r="H59" t="n">
-        <v>12</v>
-      </c>
-      <c r="I59" t="n">
+      <c r="N59" t="n">
+        <v>6</v>
+      </c>
+      <c r="O59" t="n">
         <v>11</v>
       </c>
-      <c r="J59" t="n">
+      <c r="P59" t="n">
         <v>16</v>
-      </c>
-      <c r="K59" t="n">
-        <v>12</v>
-      </c>
-      <c r="L59" t="n">
-        <v>14</v>
-      </c>
-      <c r="M59" t="n">
-        <v>64</v>
-      </c>
-      <c r="N59" t="n">
-        <v>12</v>
-      </c>
-      <c r="O59" t="n">
-        <v>13</v>
-      </c>
-      <c r="P59" t="n">
-        <v>14</v>
       </c>
       <c r="Q59" t="n">
         <v>16</v>
       </c>
       <c r="R59" t="n">
-        <v>0.049261</v>
+        <v>0.19001</v>
       </c>
       <c r="S59" t="n">
-        <v>0.100032</v>
+        <v>0.062949</v>
       </c>
       <c r="T59" t="n">
-        <v>0.09851600000000001</v>
+        <v>0.206003</v>
       </c>
       <c r="U59" t="n">
-        <v>0.143371</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>0.158523</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0.250763</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>0.196608</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.218596</v>
+        <v>0.331717</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.071177</v>
+        <v>0.478779</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.235421</v>
+        <v>0.505449</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.227205</v>
+        <v>0.835799</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.183132</v>
+        <v>0.807243</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.219258</v>
+        <v>0.6794289999999999</v>
       </c>
       <c r="AE59" t="n">
-        <v>0.242451</v>
+        <v>0.315183</v>
       </c>
       <c r="AF59" t="n">
         <v>0.259109</v>
       </c>
       <c r="AG59" t="n">
-        <v>33.333333</v>
+        <v>166.666667</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -6981,105 +6869,103 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>REPARAÇÃO E MANUTENÇÃO DE EQUIPAMENTOS DE INFORMÁTICA E COMUNICAÇÃO E DE OBJETOS PESSOAIS E DOMÉSTICOS</t>
+          <t>ATIVIDADES DE ORGANIZAÇÕES ASSOCIATIVAS</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M60" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O60" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>0.049261</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>0.100032</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>0.09851600000000001</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>0.143371</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>0.158523</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>0.250763</v>
       </c>
       <c r="X60" t="n">
-        <v>0.167331</v>
+        <v>0.196608</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>0.218596</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.445953</v>
+        <v>1.071177</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>0.235421</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.329208</v>
+        <v>0.227205</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>0.183132</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.188779</v>
+        <v>0.219258</v>
       </c>
       <c r="AE60" t="n">
-        <v>0.087021</v>
+        <v>0.242451</v>
       </c>
       <c r="AF60" t="n">
-        <v>0.016194</v>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.259109</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>33.333333</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
@@ -7095,11 +6981,11 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OUTRAS ATIVIDADES DE SERVIÇOS PESSOAIS</t>
+          <t>REPARAÇÃO E MANUTENÇÃO DE EQUIPAMENTOS DE INFORMÁTICA E COMUNICAÇÃO E DE OBJETOS PESSOAIS E DOMÉSTICOS</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -7118,28 +7004,28 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
         <v>1</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
         <v>3</v>
       </c>
-      <c r="L61" t="n">
-        <v>7</v>
-      </c>
-      <c r="M61" t="n">
-        <v>2</v>
-      </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>2</v>
       </c>
       <c r="P61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -7157,153 +7043,267 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>0.073908</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>0.178911</v>
+        <v>0.167331</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.394078</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.115442</v>
+        <v>0.445953</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.08026700000000001</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.127331</v>
+        <v>0.329208</v>
       </c>
       <c r="AC61" t="n">
-        <v>0.14794</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.261609</v>
+        <v>0.188779</v>
       </c>
       <c r="AE61" t="n">
-        <v>0.106114</v>
+        <v>0.087021</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.080972</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>400</v>
+        <v>0.016194</v>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>96</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>OUTRAS ATIVIDADES DE SERVIÇOS PESSOAIS</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3</v>
+      </c>
+      <c r="L62" t="n">
+        <v>7</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>2</v>
+      </c>
+      <c r="P62" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>5</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0.073908</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0.178911</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0.394078</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.115442</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0.08026700000000001</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.127331</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0.14794</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.261609</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0.106114</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0.080972</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>400</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C63" t="n">
         <v>97</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
         <v>1</v>
       </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
         <v>0.805986</v>
       </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
         <v>0.061999</v>
       </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="inlineStr">
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AH62" t="inlineStr">
+      <c r="AH63" t="inlineStr">
         <is>
           <t>1/12</t>
         </is>
